--- a/Game and Music Store Docs/User Stories.xlsx
+++ b/Game and Music Store Docs/User Stories.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryanc\Desktop\final_year_project\DBMS Game Store Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryanc\Desktop\final_year_project\Game and Music Store Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03F2BC8-9806-4DDB-8FB0-FD3B06323398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E017CB27-2BA5-4D9E-A38A-A04D56D4BE71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15015" yWindow="1245" windowWidth="12510" windowHeight="12750" xr2:uid="{91133E6D-6CC4-4AFD-BF36-5C9837FF4593}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{91133E6D-6CC4-4AFD-BF36-5C9837FF4593}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="244">
   <si>
     <t>As a admin,</t>
   </si>
@@ -458,66 +458,6 @@
     <t>Verify order number is displayed.</t>
   </si>
   <si>
-    <t>so I can let different accounts see different info.</t>
-  </si>
-  <si>
-    <t>so I can check the details with the database.</t>
-  </si>
-  <si>
-    <t>Verify manager name and email log in information is created.</t>
-  </si>
-  <si>
-    <t>Verify employee name and email log in information is created.</t>
-  </si>
-  <si>
-    <t>Verify customer name and email log in information is created.</t>
-  </si>
-  <si>
-    <t>Verify manager name and email log in information is read.</t>
-  </si>
-  <si>
-    <t>Verify employee name and email log in information is read.</t>
-  </si>
-  <si>
-    <t>Verify customer name and email log in information is read.</t>
-  </si>
-  <si>
-    <t>Verify manager name and email log in information is updated.</t>
-  </si>
-  <si>
-    <t>Verify employee name and email log in information is updated.</t>
-  </si>
-  <si>
-    <t>Verify customer name and email log in information is updated.</t>
-  </si>
-  <si>
-    <t>Verify manager name and email log in information is deleted.</t>
-  </si>
-  <si>
-    <t>Verify employee name and email log in information is deleted.</t>
-  </si>
-  <si>
-    <t>Verify customer name and email log in information is deleted.</t>
-  </si>
-  <si>
-    <t>I want to create a login,</t>
-  </si>
-  <si>
-    <t>I want to read login details,</t>
-  </si>
-  <si>
-    <t>I want to update login details,</t>
-  </si>
-  <si>
-    <t>I want to delete login details,</t>
-  </si>
-  <si>
-    <t>so I can change personal data .</t>
-  </si>
-  <si>
-    <t>so I can remove unnecessary details.</t>
-  </si>
-  <si>
     <t>so I can let customers buy games and music.</t>
   </si>
   <si>
@@ -795,6 +735,39 @@
   </si>
   <si>
     <t>Verify payment date and time is read for album.</t>
+  </si>
+  <si>
+    <t>Verify manager's password is read.</t>
+  </si>
+  <si>
+    <t>Verify manager's password is updated.</t>
+  </si>
+  <si>
+    <t>Verify manager's name is deleted.</t>
+  </si>
+  <si>
+    <t>Verify manager's phone number is deleted.</t>
+  </si>
+  <si>
+    <t>Verify manager's email is deleted.</t>
+  </si>
+  <si>
+    <t>Verify manager's password is deleted.</t>
+  </si>
+  <si>
+    <t>Verify employee's password is read.</t>
+  </si>
+  <si>
+    <t>Verify employee's password is updated.</t>
+  </si>
+  <si>
+    <t>Verify employee's password is deleted.</t>
+  </si>
+  <si>
+    <t>Verify manager's password is created 0&gt; &amp; &lt;10.</t>
+  </si>
+  <si>
+    <t>Verify employee's password is created 0&gt; &amp; &lt;10.</t>
   </si>
 </sst>
 </file>
@@ -810,7 +783,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -871,12 +844,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -901,7 +868,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1236,314 +1203,350 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62F77FC3-F402-4BE8-8A68-6767566B15A6}">
-  <dimension ref="A1:K251"/>
+  <dimension ref="A1:K240"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
+      <c r="A14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
+      <c r="A15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
-        <v>2</v>
+        <v>237</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -1552,15 +1555,13 @@
       <c r="K22" s="1"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1" t="s">
-        <v>47</v>
+        <v>238</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
@@ -1568,274 +1569,287 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
@@ -1846,7 +1860,7 @@
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -1856,14 +1870,14 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -1873,14 +1887,14 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -1895,7 +1909,7 @@
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -1909,247 +1923,262 @@
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
+      <c r="F47" s="2" t="s">
+        <v>241</v>
+      </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="7"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="7"/>
+      <c r="J52" s="7"/>
+      <c r="K52" s="7"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="7"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="G53" s="7"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="7"/>
+      <c r="J53" s="7"/>
+      <c r="K53" s="7"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="7"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
+      <c r="K54" s="7"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="7"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="7"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+      <c r="K56" s="7"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+      <c r="J57" s="7"/>
+      <c r="K57" s="7"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="7"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7"/>
+      <c r="K58" s="7"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="7"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="7"/>
+      <c r="K59" s="7"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="7"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
+      <c r="B61" s="7"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G61" s="7"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7"/>
+      <c r="J61" s="7"/>
+      <c r="K61" s="7"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B62" s="7"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="7"/>
+      <c r="K62" s="7"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
+      <c r="J63" s="7"/>
+      <c r="K63" s="7"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
-        <v>0</v>
-      </c>
+      <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
       <c r="E64" s="7"/>
       <c r="F64" s="7" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
@@ -2158,15 +2187,13 @@
       <c r="K64" s="7"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
-        <v>60</v>
-      </c>
+      <c r="A65" s="7"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
       <c r="E65" s="7"/>
       <c r="F65" s="7" t="s">
-        <v>65</v>
+        <v>240</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
@@ -2175,16 +2202,12 @@
       <c r="K65" s="7"/>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="s">
-        <v>1</v>
-      </c>
+      <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
       <c r="E66" s="7"/>
-      <c r="F66" s="7" t="s">
-        <v>66</v>
-      </c>
+      <c r="F66" s="7"/>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
       <c r="I66" s="7"/>
@@ -2192,13 +2215,15 @@
       <c r="K66" s="7"/>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67" s="7"/>
+      <c r="A67" s="7" t="s">
+        <v>0</v>
+      </c>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
       <c r="E67" s="7"/>
       <c r="F67" s="7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
@@ -2207,12 +2232,16 @@
       <c r="K67" s="7"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="7"/>
+      <c r="A68" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
       <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
+      <c r="F68" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
       <c r="I68" s="7"/>
@@ -2221,14 +2250,14 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
       <c r="E69" s="7"/>
       <c r="F69" s="7" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
@@ -2237,15 +2266,13 @@
       <c r="K69" s="7"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="s">
-        <v>61</v>
-      </c>
+      <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
       <c r="E70" s="7"/>
       <c r="F70" s="7" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
@@ -2254,15 +2281,13 @@
       <c r="K70" s="7"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>4</v>
-      </c>
+      <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
       <c r="E71" s="7"/>
       <c r="F71" s="7" t="s">
-        <v>70</v>
+        <v>241</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
@@ -2271,188 +2296,205 @@
       <c r="K71" s="7"/>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" s="7"/>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G72" s="7"/>
-      <c r="H72" s="7"/>
-      <c r="I72" s="7"/>
-      <c r="J72" s="7"/>
-      <c r="K72" s="7"/>
+      <c r="A72" s="10"/>
+      <c r="B72" s="10"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="10"/>
+      <c r="E72" s="10"/>
+      <c r="F72" s="10"/>
+      <c r="G72" s="10"/>
+      <c r="H72" s="10"/>
+      <c r="I72" s="10"/>
+      <c r="J72" s="10"/>
+      <c r="K72" s="10"/>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="7"/>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7"/>
-      <c r="G73" s="7"/>
-      <c r="H73" s="7"/>
-      <c r="I73" s="7"/>
-      <c r="J73" s="7"/>
-      <c r="K73" s="7"/>
+      <c r="F73" s="10"/>
+      <c r="G73" s="10"/>
+      <c r="H73" s="10"/>
+      <c r="I73" s="10"/>
+      <c r="J73" s="10"/>
+      <c r="K73" s="10"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
+      <c r="A74" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A75" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G75" s="7"/>
-      <c r="H75" s="7"/>
-      <c r="I75" s="7"/>
-      <c r="J75" s="7"/>
-      <c r="K75" s="7"/>
+      <c r="A75" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3"/>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
-      <c r="J76" s="7"/>
-      <c r="K76" s="7"/>
+      <c r="A76" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G77" s="7"/>
-      <c r="H77" s="7"/>
-      <c r="I77" s="7"/>
-      <c r="J77" s="7"/>
-      <c r="K77" s="7"/>
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3"/>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78" s="7"/>
-      <c r="B78" s="7"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="7"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="7"/>
-      <c r="G78" s="7"/>
-      <c r="H78" s="7"/>
-      <c r="I78" s="7"/>
-      <c r="J78" s="7"/>
-      <c r="K78" s="7"/>
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3"/>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B79" s="7"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G79" s="7"/>
-      <c r="H79" s="7"/>
-      <c r="I79" s="7"/>
-      <c r="J79" s="7"/>
-      <c r="K79" s="7"/>
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="3"/>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B80" s="7"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G80" s="7"/>
-      <c r="H80" s="7"/>
-      <c r="I80" s="7"/>
-      <c r="J80" s="7"/>
-      <c r="K80" s="7"/>
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3"/>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G81" s="7"/>
-      <c r="H81" s="7"/>
-      <c r="I81" s="7"/>
-      <c r="J81" s="7"/>
-      <c r="K81" s="7"/>
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="3"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="3"/>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82" s="7"/>
-      <c r="B82" s="7"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="G82" s="7"/>
-      <c r="H82" s="7"/>
-      <c r="I82" s="7"/>
-      <c r="J82" s="7"/>
-      <c r="K82" s="7"/>
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="3"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="3"/>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3"/>
+      <c r="I83" s="3"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="3"/>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="3"/>
+      <c r="J84" s="3"/>
+      <c r="K84" s="3"/>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3" t="s">
-        <v>111</v>
+        <v>174</v>
       </c>
       <c r="G85" s="3"/>
       <c r="H85" s="3"/>
@@ -2461,15 +2503,13 @@
       <c r="K85" s="3"/>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
-        <v>56</v>
-      </c>
+      <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3" t="s">
-        <v>93</v>
+        <v>175</v>
       </c>
       <c r="G86" s="3"/>
       <c r="H86" s="3"/>
@@ -2478,15 +2518,13 @@
       <c r="K86" s="3"/>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
-        <v>18</v>
-      </c>
+      <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
-        <v>97</v>
+        <v>176</v>
       </c>
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
@@ -2501,7 +2539,7 @@
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3" t="s">
-        <v>98</v>
+        <v>177</v>
       </c>
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
@@ -2516,7 +2554,7 @@
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
@@ -2530,9 +2568,7 @@
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
-      <c r="F90" s="3" t="s">
-        <v>112</v>
-      </c>
+      <c r="F90" s="3"/>
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
@@ -2540,13 +2576,15 @@
       <c r="K90" s="3"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91" s="3"/>
+      <c r="A91" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="G91" s="3"/>
       <c r="H91" s="3"/>
@@ -2555,13 +2593,15 @@
       <c r="K91" s="3"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" s="3"/>
+      <c r="A92" s="3" t="s">
+        <v>57</v>
+      </c>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3" t="s">
-        <v>169</v>
+        <v>94</v>
       </c>
       <c r="G92" s="3"/>
       <c r="H92" s="3"/>
@@ -2570,13 +2610,15 @@
       <c r="K92" s="3"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A93" s="3"/>
+      <c r="A93" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
@@ -2591,7 +2633,7 @@
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
@@ -2606,7 +2648,7 @@
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3" t="s">
-        <v>171</v>
+        <v>109</v>
       </c>
       <c r="G95" s="3"/>
       <c r="H95" s="3"/>
@@ -2621,7 +2663,7 @@
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3" t="s">
-        <v>194</v>
+        <v>115</v>
       </c>
       <c r="G96" s="3"/>
       <c r="H96" s="3"/>
@@ -2636,7 +2678,7 @@
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3" t="s">
-        <v>195</v>
+        <v>116</v>
       </c>
       <c r="G97" s="3"/>
       <c r="H97" s="3"/>
@@ -2651,7 +2693,7 @@
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="G98" s="3"/>
       <c r="H98" s="3"/>
@@ -2666,7 +2708,7 @@
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3" t="s">
-        <v>197</v>
+        <v>117</v>
       </c>
       <c r="G99" s="3"/>
       <c r="H99" s="3"/>
@@ -2681,7 +2723,7 @@
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="G100" s="3"/>
       <c r="H100" s="3"/>
@@ -2695,7 +2737,9 @@
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
-      <c r="F101" s="3"/>
+      <c r="F101" s="3" t="s">
+        <v>152</v>
+      </c>
       <c r="G101" s="3"/>
       <c r="H101" s="3"/>
       <c r="I101" s="3"/>
@@ -2703,15 +2747,13 @@
       <c r="K101" s="3"/>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
       <c r="F102" s="3" t="s">
-        <v>99</v>
+        <v>178</v>
       </c>
       <c r="G102" s="3"/>
       <c r="H102" s="3"/>
@@ -2720,15 +2762,13 @@
       <c r="K102" s="3"/>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
       <c r="F103" s="3" t="s">
-        <v>94</v>
+        <v>179</v>
       </c>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -2737,15 +2777,13 @@
       <c r="K103" s="3"/>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
       <c r="F104" s="3" t="s">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -2760,7 +2798,7 @@
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
       <c r="F105" s="3" t="s">
-        <v>101</v>
+        <v>181</v>
       </c>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -2775,7 +2813,7 @@
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
       <c r="F106" s="3" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -2789,9 +2827,7 @@
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
-      <c r="F107" s="3" t="s">
-        <v>115</v>
-      </c>
+      <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
       <c r="I107" s="3"/>
@@ -2799,13 +2835,15 @@
       <c r="K107" s="3"/>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" s="3"/>
+      <c r="A108" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
       <c r="F108" s="3" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -2814,13 +2852,15 @@
       <c r="K108" s="3"/>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" s="3"/>
+      <c r="A109" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
       <c r="F109" s="3" t="s">
-        <v>192</v>
+        <v>95</v>
       </c>
       <c r="G109" s="3"/>
       <c r="H109" s="3"/>
@@ -2829,13 +2869,15 @@
       <c r="K109" s="3"/>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A110" s="3"/>
+      <c r="A110" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
       <c r="F110" s="3" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="G110" s="3"/>
       <c r="H110" s="3"/>
@@ -2850,7 +2892,7 @@
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
       <c r="F111" s="3" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="G111" s="3"/>
       <c r="H111" s="3"/>
@@ -2865,7 +2907,7 @@
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
       <c r="F112" s="3" t="s">
-        <v>172</v>
+        <v>110</v>
       </c>
       <c r="G112" s="3"/>
       <c r="H112" s="3"/>
@@ -2880,7 +2922,7 @@
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
       <c r="F113" s="3" t="s">
-        <v>198</v>
+        <v>119</v>
       </c>
       <c r="G113" s="3"/>
       <c r="H113" s="3"/>
@@ -2895,7 +2937,7 @@
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
       <c r="F114" s="3" t="s">
-        <v>199</v>
+        <v>120</v>
       </c>
       <c r="G114" s="3"/>
       <c r="H114" s="3"/>
@@ -2910,7 +2952,7 @@
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
       <c r="F115" s="3" t="s">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G115" s="3"/>
       <c r="H115" s="3"/>
@@ -2925,7 +2967,7 @@
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
       <c r="F116" s="3" t="s">
-        <v>201</v>
+        <v>121</v>
       </c>
       <c r="G116" s="3"/>
       <c r="H116" s="3"/>
@@ -2940,7 +2982,7 @@
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
       <c r="F117" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="G117" s="3"/>
       <c r="H117" s="3"/>
@@ -2954,7 +2996,9 @@
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
-      <c r="F118" s="3"/>
+      <c r="F118" s="3" t="s">
+        <v>153</v>
+      </c>
       <c r="G118" s="3"/>
       <c r="H118" s="3"/>
       <c r="I118" s="3"/>
@@ -2962,15 +3006,13 @@
       <c r="K118" s="3"/>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A119" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
       <c r="F119" s="3" t="s">
-        <v>102</v>
+        <v>182</v>
       </c>
       <c r="G119" s="3"/>
       <c r="H119" s="3"/>
@@ -2979,15 +3021,13 @@
       <c r="K119" s="3"/>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120" s="3" t="s">
-        <v>58</v>
-      </c>
+      <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
       <c r="F120" s="3" t="s">
-        <v>95</v>
+        <v>183</v>
       </c>
       <c r="G120" s="3"/>
       <c r="H120" s="3"/>
@@ -2996,15 +3036,13 @@
       <c r="K120" s="3"/>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A121" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
       <c r="F121" s="3" t="s">
-        <v>103</v>
+        <v>184</v>
       </c>
       <c r="G121" s="3"/>
       <c r="H121" s="3"/>
@@ -3019,7 +3057,7 @@
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
       <c r="F122" s="3" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="G122" s="3"/>
       <c r="H122" s="3"/>
@@ -3034,7 +3072,7 @@
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
       <c r="F123" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="G123" s="3"/>
       <c r="H123" s="3"/>
@@ -3048,9 +3086,7 @@
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
-      <c r="F124" s="3" t="s">
-        <v>119</v>
-      </c>
+      <c r="F124" s="3"/>
       <c r="G124" s="3"/>
       <c r="H124" s="3"/>
       <c r="I124" s="3"/>
@@ -3058,13 +3094,15 @@
       <c r="K124" s="3"/>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A125" s="3"/>
+      <c r="A125" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
       <c r="F125" s="3" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="G125" s="3"/>
       <c r="H125" s="3"/>
@@ -3073,13 +3111,15 @@
       <c r="K125" s="3"/>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A126" s="3"/>
+      <c r="A126" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
       <c r="F126" s="3" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
       <c r="G126" s="3"/>
       <c r="H126" s="3"/>
@@ -3088,13 +3128,15 @@
       <c r="K126" s="3"/>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A127" s="3"/>
+      <c r="A127" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
       <c r="F127" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="G127" s="3"/>
       <c r="H127" s="3"/>
@@ -3109,7 +3151,7 @@
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
       <c r="F128" s="3" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="G128" s="3"/>
       <c r="H128" s="3"/>
@@ -3124,7 +3166,7 @@
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
       <c r="F129" s="3" t="s">
-        <v>173</v>
+        <v>22</v>
       </c>
       <c r="G129" s="3"/>
       <c r="H129" s="3"/>
@@ -3139,7 +3181,7 @@
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
       <c r="F130" s="3" t="s">
-        <v>202</v>
+        <v>123</v>
       </c>
       <c r="G130" s="3"/>
       <c r="H130" s="3"/>
@@ -3154,7 +3196,7 @@
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
       <c r="F131" s="3" t="s">
-        <v>203</v>
+        <v>124</v>
       </c>
       <c r="G131" s="3"/>
       <c r="H131" s="3"/>
@@ -3169,7 +3211,7 @@
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
       <c r="F132" s="3" t="s">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="G132" s="3"/>
       <c r="H132" s="3"/>
@@ -3184,7 +3226,7 @@
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
       <c r="F133" s="3" t="s">
-        <v>205</v>
+        <v>125</v>
       </c>
       <c r="G133" s="3"/>
       <c r="H133" s="3"/>
@@ -3199,7 +3241,7 @@
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
       <c r="F134" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G134" s="3"/>
       <c r="H134" s="3"/>
@@ -3213,7 +3255,9 @@
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
-      <c r="F135" s="3"/>
+      <c r="F135" s="3" t="s">
+        <v>154</v>
+      </c>
       <c r="G135" s="3"/>
       <c r="H135" s="3"/>
       <c r="I135" s="3"/>
@@ -3221,15 +3265,13 @@
       <c r="K135" s="3"/>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A136" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
       <c r="F136" s="3" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="G136" s="3"/>
       <c r="H136" s="3"/>
@@ -3238,15 +3280,13 @@
       <c r="K136" s="3"/>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A137" s="3" t="s">
-        <v>59</v>
-      </c>
+      <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
       <c r="F137" s="3" t="s">
-        <v>96</v>
+        <v>187</v>
       </c>
       <c r="G137" s="3"/>
       <c r="H137" s="3"/>
@@ -3255,15 +3295,13 @@
       <c r="K137" s="3"/>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A138" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
       <c r="F138" s="3" t="s">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="G138" s="3"/>
       <c r="H138" s="3"/>
@@ -3278,7 +3316,7 @@
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
       <c r="F139" s="3" t="s">
-        <v>107</v>
+        <v>189</v>
       </c>
       <c r="G139" s="3"/>
       <c r="H139" s="3"/>
@@ -3293,7 +3331,7 @@
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
       <c r="F140" s="3" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="G140" s="3"/>
       <c r="H140" s="3"/>
@@ -3301,293 +3339,299 @@
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A141" s="3"/>
-      <c r="B141" s="3"/>
-      <c r="C141" s="3"/>
-      <c r="D141" s="3"/>
-      <c r="E141" s="3"/>
-      <c r="F141" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G141" s="3"/>
-      <c r="H141" s="3"/>
-      <c r="I141" s="3"/>
-      <c r="J141" s="3"/>
-      <c r="K141" s="3"/>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A142" s="3"/>
-      <c r="B142" s="3"/>
-      <c r="C142" s="3"/>
-      <c r="D142" s="3"/>
-      <c r="E142" s="3"/>
-      <c r="F142" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G142" s="3"/>
-      <c r="H142" s="3"/>
-      <c r="I142" s="3"/>
-      <c r="J142" s="3"/>
-      <c r="K142" s="3"/>
-    </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A143" s="3"/>
-      <c r="B143" s="3"/>
-      <c r="C143" s="3"/>
-      <c r="D143" s="3"/>
-      <c r="E143" s="3"/>
-      <c r="F143" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G143" s="3"/>
-      <c r="H143" s="3"/>
-      <c r="I143" s="3"/>
-      <c r="J143" s="3"/>
-      <c r="K143" s="3"/>
+      <c r="A143" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B143" s="4"/>
+      <c r="C143" s="4"/>
+      <c r="D143" s="4"/>
+      <c r="E143" s="4"/>
+      <c r="F143" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G143" s="4"/>
+      <c r="H143" s="4"/>
+      <c r="I143" s="4"/>
+      <c r="J143" s="4"/>
+      <c r="K143" s="4"/>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A144" s="3"/>
-      <c r="B144" s="3"/>
-      <c r="C144" s="3"/>
-      <c r="D144" s="3"/>
-      <c r="E144" s="3"/>
-      <c r="F144" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="G144" s="3"/>
-      <c r="H144" s="3"/>
-      <c r="I144" s="3"/>
-      <c r="J144" s="3"/>
-      <c r="K144" s="3"/>
+      <c r="A144" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B144" s="4"/>
+      <c r="C144" s="4"/>
+      <c r="D144" s="4"/>
+      <c r="E144" s="4"/>
+      <c r="F144" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G144" s="4"/>
+      <c r="H144" s="4"/>
+      <c r="I144" s="4"/>
+      <c r="J144" s="4"/>
+      <c r="K144" s="4"/>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A145" s="3"/>
-      <c r="B145" s="3"/>
-      <c r="C145" s="3"/>
-      <c r="D145" s="3"/>
-      <c r="E145" s="3"/>
-      <c r="F145" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="G145" s="3"/>
-      <c r="H145" s="3"/>
-      <c r="I145" s="3"/>
-      <c r="J145" s="3"/>
-      <c r="K145" s="3"/>
+      <c r="A145" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B145" s="4"/>
+      <c r="C145" s="4"/>
+      <c r="D145" s="4"/>
+      <c r="E145" s="4"/>
+      <c r="F145" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G145" s="4"/>
+      <c r="H145" s="4"/>
+      <c r="I145" s="4"/>
+      <c r="J145" s="4"/>
+      <c r="K145" s="4"/>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A146" s="3"/>
-      <c r="B146" s="3"/>
-      <c r="C146" s="3"/>
-      <c r="D146" s="3"/>
-      <c r="E146" s="3"/>
-      <c r="F146" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="G146" s="3"/>
-      <c r="H146" s="3"/>
-      <c r="I146" s="3"/>
-      <c r="J146" s="3"/>
-      <c r="K146" s="3"/>
+      <c r="A146" s="4"/>
+      <c r="B146" s="4"/>
+      <c r="C146" s="4"/>
+      <c r="D146" s="4"/>
+      <c r="E146" s="4"/>
+      <c r="F146" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G146" s="4"/>
+      <c r="H146" s="4"/>
+      <c r="I146" s="4"/>
+      <c r="J146" s="4"/>
+      <c r="K146" s="4"/>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A147" s="3"/>
-      <c r="B147" s="3"/>
-      <c r="C147" s="3"/>
-      <c r="D147" s="3"/>
-      <c r="E147" s="3"/>
-      <c r="F147" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G147" s="3"/>
-      <c r="H147" s="3"/>
-      <c r="I147" s="3"/>
-      <c r="J147" s="3"/>
-      <c r="K147" s="3"/>
+      <c r="A147" s="4"/>
+      <c r="B147" s="4"/>
+      <c r="C147" s="4"/>
+      <c r="D147" s="4"/>
+      <c r="E147" s="4"/>
+      <c r="F147" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G147" s="4"/>
+      <c r="H147" s="4"/>
+      <c r="I147" s="4"/>
+      <c r="J147" s="4"/>
+      <c r="K147" s="4"/>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A148" s="3"/>
-      <c r="B148" s="3"/>
-      <c r="C148" s="3"/>
-      <c r="D148" s="3"/>
-      <c r="E148" s="3"/>
-      <c r="F148" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G148" s="3"/>
-      <c r="H148" s="3"/>
-      <c r="I148" s="3"/>
-      <c r="J148" s="3"/>
-      <c r="K148" s="3"/>
+      <c r="A148" s="4"/>
+      <c r="B148" s="4"/>
+      <c r="C148" s="4"/>
+      <c r="D148" s="4"/>
+      <c r="E148" s="4"/>
+      <c r="F148" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G148" s="4"/>
+      <c r="H148" s="4"/>
+      <c r="I148" s="4"/>
+      <c r="J148" s="4"/>
+      <c r="K148" s="4"/>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A149" s="3"/>
-      <c r="B149" s="3"/>
-      <c r="C149" s="3"/>
-      <c r="D149" s="3"/>
-      <c r="E149" s="3"/>
-      <c r="F149" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="G149" s="3"/>
-      <c r="H149" s="3"/>
-      <c r="I149" s="3"/>
-      <c r="J149" s="3"/>
-      <c r="K149" s="3"/>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A150" s="3"/>
-      <c r="B150" s="3"/>
-      <c r="C150" s="3"/>
-      <c r="D150" s="3"/>
-      <c r="E150" s="3"/>
-      <c r="F150" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="G150" s="3"/>
-      <c r="H150" s="3"/>
-      <c r="I150" s="3"/>
-      <c r="J150" s="3"/>
-      <c r="K150" s="3"/>
+      <c r="A149" s="4"/>
+      <c r="B149" s="4"/>
+      <c r="C149" s="4"/>
+      <c r="D149" s="4"/>
+      <c r="E149" s="4"/>
+      <c r="F149" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G149" s="4"/>
+      <c r="H149" s="4"/>
+      <c r="I149" s="4"/>
+      <c r="J149" s="4"/>
+      <c r="K149" s="4"/>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A151" s="3"/>
-      <c r="B151" s="3"/>
-      <c r="C151" s="3"/>
-      <c r="D151" s="3"/>
-      <c r="E151" s="3"/>
-      <c r="F151" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G151" s="3"/>
-      <c r="H151" s="3"/>
-      <c r="I151" s="3"/>
-      <c r="J151" s="3"/>
-      <c r="K151" s="3"/>
+      <c r="A151" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B151" s="5"/>
+      <c r="C151" s="5"/>
+      <c r="D151" s="5"/>
+      <c r="E151" s="5"/>
+      <c r="F151" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="G151" s="5"/>
+      <c r="H151" s="5"/>
+      <c r="I151" s="5"/>
+      <c r="J151" s="5"/>
+      <c r="K151" s="5"/>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A152" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B152" s="5"/>
+      <c r="C152" s="5"/>
+      <c r="D152" s="5"/>
+      <c r="E152" s="5"/>
+      <c r="F152" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G152" s="5"/>
+      <c r="H152" s="5"/>
+      <c r="I152" s="5"/>
+      <c r="J152" s="5"/>
+      <c r="K152" s="5"/>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A153" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B153" s="5"/>
+      <c r="C153" s="5"/>
+      <c r="D153" s="5"/>
+      <c r="E153" s="5"/>
+      <c r="F153" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G153" s="5"/>
+      <c r="H153" s="5"/>
+      <c r="I153" s="5"/>
+      <c r="J153" s="5"/>
+      <c r="K153" s="5"/>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A154" s="4" t="s">
+      <c r="A154" s="5"/>
+      <c r="B154" s="5"/>
+      <c r="C154" s="5"/>
+      <c r="D154" s="5"/>
+      <c r="E154" s="5"/>
+      <c r="F154" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G154" s="5"/>
+      <c r="H154" s="5"/>
+      <c r="I154" s="5"/>
+      <c r="J154" s="5"/>
+      <c r="K154" s="5"/>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A155" s="5"/>
+      <c r="B155" s="5"/>
+      <c r="C155" s="5"/>
+      <c r="D155" s="5"/>
+      <c r="E155" s="5"/>
+      <c r="F155" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="G155" s="5"/>
+      <c r="H155" s="5"/>
+      <c r="I155" s="5"/>
+      <c r="J155" s="5"/>
+      <c r="K155" s="5"/>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A156" s="5"/>
+      <c r="B156" s="5"/>
+      <c r="C156" s="5"/>
+      <c r="D156" s="5"/>
+      <c r="E156" s="5"/>
+      <c r="F156" s="5"/>
+      <c r="G156" s="5"/>
+      <c r="H156" s="5"/>
+      <c r="I156" s="5"/>
+      <c r="J156" s="5"/>
+      <c r="K156" s="5"/>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A157" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B154" s="4"/>
-      <c r="C154" s="4"/>
-      <c r="D154" s="4"/>
-      <c r="E154" s="4"/>
-      <c r="F154" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G154" s="4"/>
-      <c r="H154" s="4"/>
-      <c r="I154" s="4"/>
-      <c r="J154" s="4"/>
-      <c r="K154" s="4"/>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A155" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B155" s="4"/>
-      <c r="C155" s="4"/>
-      <c r="D155" s="4"/>
-      <c r="E155" s="4"/>
-      <c r="F155" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="G155" s="4"/>
-      <c r="H155" s="4"/>
-      <c r="I155" s="4"/>
-      <c r="J155" s="4"/>
-      <c r="K155" s="4"/>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A156" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B156" s="4"/>
-      <c r="C156" s="4"/>
-      <c r="D156" s="4"/>
-      <c r="E156" s="4"/>
-      <c r="F156" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="G156" s="4"/>
-      <c r="H156" s="4"/>
-      <c r="I156" s="4"/>
-      <c r="J156" s="4"/>
-      <c r="K156" s="4"/>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A157" s="4"/>
-      <c r="B157" s="4"/>
-      <c r="C157" s="4"/>
-      <c r="D157" s="4"/>
-      <c r="E157" s="4"/>
-      <c r="F157" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G157" s="4"/>
-      <c r="H157" s="4"/>
-      <c r="I157" s="4"/>
-      <c r="J157" s="4"/>
-      <c r="K157" s="4"/>
+      <c r="B157" s="5"/>
+      <c r="C157" s="5"/>
+      <c r="D157" s="5"/>
+      <c r="E157" s="5"/>
+      <c r="F157" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="G157" s="5"/>
+      <c r="H157" s="5"/>
+      <c r="I157" s="5"/>
+      <c r="J157" s="5"/>
+      <c r="K157" s="5"/>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A158" s="4"/>
-      <c r="B158" s="4"/>
-      <c r="C158" s="4"/>
-      <c r="D158" s="4"/>
-      <c r="E158" s="4"/>
-      <c r="F158" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="G158" s="4"/>
-      <c r="H158" s="4"/>
-      <c r="I158" s="4"/>
-      <c r="J158" s="4"/>
-      <c r="K158" s="4"/>
+      <c r="A158" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B158" s="5"/>
+      <c r="C158" s="5"/>
+      <c r="D158" s="5"/>
+      <c r="E158" s="5"/>
+      <c r="F158" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G158" s="5"/>
+      <c r="H158" s="5"/>
+      <c r="I158" s="5"/>
+      <c r="J158" s="5"/>
+      <c r="K158" s="5"/>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A159" s="4"/>
-      <c r="B159" s="4"/>
-      <c r="C159" s="4"/>
-      <c r="D159" s="4"/>
-      <c r="E159" s="4"/>
-      <c r="F159" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="G159" s="4"/>
-      <c r="H159" s="4"/>
-      <c r="I159" s="4"/>
-      <c r="J159" s="4"/>
-      <c r="K159" s="4"/>
+      <c r="A159" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B159" s="5"/>
+      <c r="C159" s="5"/>
+      <c r="D159" s="5"/>
+      <c r="E159" s="5"/>
+      <c r="F159" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="G159" s="5"/>
+      <c r="H159" s="5"/>
+      <c r="I159" s="5"/>
+      <c r="J159" s="5"/>
+      <c r="K159" s="5"/>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A160" s="4"/>
-      <c r="B160" s="4"/>
-      <c r="C160" s="4"/>
-      <c r="D160" s="4"/>
-      <c r="E160" s="4"/>
-      <c r="F160" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="G160" s="4"/>
-      <c r="H160" s="4"/>
-      <c r="I160" s="4"/>
-      <c r="J160" s="4"/>
-      <c r="K160" s="4"/>
+      <c r="A160" s="5"/>
+      <c r="B160" s="5"/>
+      <c r="C160" s="5"/>
+      <c r="D160" s="5"/>
+      <c r="E160" s="5"/>
+      <c r="F160" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="G160" s="5"/>
+      <c r="H160" s="5"/>
+      <c r="I160" s="5"/>
+      <c r="J160" s="5"/>
+      <c r="K160" s="5"/>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A161" s="5"/>
+      <c r="B161" s="5"/>
+      <c r="C161" s="5"/>
+      <c r="D161" s="5"/>
+      <c r="E161" s="5"/>
+      <c r="F161" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="G161" s="5"/>
+      <c r="H161" s="5"/>
+      <c r="I161" s="5"/>
+      <c r="J161" s="5"/>
+      <c r="K161" s="5"/>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A162" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="A162" s="5"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
       <c r="D162" s="5"/>
       <c r="E162" s="5"/>
-      <c r="F162" s="5" t="s">
-        <v>176</v>
-      </c>
+      <c r="F162" s="5"/>
       <c r="G162" s="5"/>
       <c r="H162" s="5"/>
       <c r="I162" s="5"/>
@@ -3596,14 +3640,14 @@
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="5" t="s">
-        <v>212</v>
+        <v>13</v>
       </c>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
       <c r="D163" s="5"/>
       <c r="E163" s="5"/>
       <c r="F163" s="5" t="s">
-        <v>216</v>
+        <v>120</v>
       </c>
       <c r="G163" s="5"/>
       <c r="H163" s="5"/>
@@ -3613,14 +3657,14 @@
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
       <c r="D164" s="5"/>
       <c r="E164" s="5"/>
       <c r="F164" s="5" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="G164" s="5"/>
       <c r="H164" s="5"/>
@@ -3629,13 +3673,15 @@
       <c r="K164" s="5"/>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A165" s="5"/>
+      <c r="A165" s="5" t="s">
+        <v>193</v>
+      </c>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
       <c r="D165" s="5"/>
       <c r="E165" s="5"/>
       <c r="F165" s="5" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="G165" s="5"/>
       <c r="H165" s="5"/>
@@ -3650,7 +3696,7 @@
       <c r="D166" s="5"/>
       <c r="E166" s="5"/>
       <c r="F166" s="5" t="s">
-        <v>211</v>
+        <v>159</v>
       </c>
       <c r="G166" s="5"/>
       <c r="H166" s="5"/>
@@ -3664,7 +3710,9 @@
       <c r="C167" s="5"/>
       <c r="D167" s="5"/>
       <c r="E167" s="5"/>
-      <c r="F167" s="5"/>
+      <c r="F167" s="5" t="s">
+        <v>199</v>
+      </c>
       <c r="G167" s="5"/>
       <c r="H167" s="5"/>
       <c r="I167" s="5"/>
@@ -3672,16 +3720,12 @@
       <c r="K167" s="5"/>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A168" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="A168" s="5"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
       <c r="D168" s="5"/>
       <c r="E168" s="5"/>
-      <c r="F168" s="5" t="s">
-        <v>116</v>
-      </c>
+      <c r="F168" s="5"/>
       <c r="G168" s="5"/>
       <c r="H168" s="5"/>
       <c r="I168" s="5"/>
@@ -3690,14 +3734,14 @@
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
       <c r="D169" s="5"/>
       <c r="E169" s="5"/>
       <c r="F169" s="5" t="s">
-        <v>192</v>
+        <v>124</v>
       </c>
       <c r="G169" s="5"/>
       <c r="H169" s="5"/>
@@ -3707,14 +3751,14 @@
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
       <c r="D170" s="5"/>
       <c r="E170" s="5"/>
       <c r="F170" s="5" t="s">
-        <v>221</v>
+        <v>173</v>
       </c>
       <c r="G170" s="5"/>
       <c r="H170" s="5"/>
@@ -3723,13 +3767,15 @@
       <c r="K170" s="5"/>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A171" s="5"/>
+      <c r="A171" s="5" t="s">
+        <v>194</v>
+      </c>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
       <c r="D171" s="5"/>
       <c r="E171" s="5"/>
       <c r="F171" s="5" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="G171" s="5"/>
       <c r="H171" s="5"/>
@@ -3744,7 +3790,7 @@
       <c r="D172" s="5"/>
       <c r="E172" s="5"/>
       <c r="F172" s="5" t="s">
-        <v>217</v>
+        <v>160</v>
       </c>
       <c r="G172" s="5"/>
       <c r="H172" s="5"/>
@@ -3758,329 +3804,325 @@
       <c r="C173" s="5"/>
       <c r="D173" s="5"/>
       <c r="E173" s="5"/>
-      <c r="F173" s="5"/>
+      <c r="F173" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="G173" s="5"/>
       <c r="H173" s="5"/>
       <c r="I173" s="5"/>
       <c r="J173" s="5"/>
       <c r="K173" s="5"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A174" s="5" t="s">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A176" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B174" s="5"/>
-      <c r="C174" s="5"/>
-      <c r="D174" s="5"/>
-      <c r="E174" s="5"/>
-      <c r="F174" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="G174" s="5"/>
-      <c r="H174" s="5"/>
-      <c r="I174" s="5"/>
-      <c r="J174" s="5"/>
-      <c r="K174" s="5"/>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A175" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B175" s="5"/>
-      <c r="C175" s="5"/>
-      <c r="D175" s="5"/>
-      <c r="E175" s="5"/>
-      <c r="F175" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="G175" s="5"/>
-      <c r="H175" s="5"/>
-      <c r="I175" s="5"/>
-      <c r="J175" s="5"/>
-      <c r="K175" s="5"/>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A176" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="B176" s="5"/>
-      <c r="C176" s="5"/>
-      <c r="D176" s="5"/>
-      <c r="E176" s="5"/>
-      <c r="F176" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="G176" s="5"/>
-      <c r="H176" s="5"/>
-      <c r="I176" s="5"/>
-      <c r="J176" s="5"/>
-      <c r="K176" s="5"/>
+      <c r="B176" s="6"/>
+      <c r="C176" s="6"/>
+      <c r="D176" s="6"/>
+      <c r="E176" s="6"/>
+      <c r="F176" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="G176" s="6"/>
+      <c r="H176" s="6"/>
+      <c r="I176" s="6"/>
+      <c r="J176" s="6"/>
+      <c r="K176" s="6"/>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A177" s="5"/>
-      <c r="B177" s="5"/>
-      <c r="C177" s="5"/>
-      <c r="D177" s="5"/>
-      <c r="E177" s="5"/>
-      <c r="F177" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="G177" s="5"/>
-      <c r="H177" s="5"/>
-      <c r="I177" s="5"/>
-      <c r="J177" s="5"/>
-      <c r="K177" s="5"/>
+      <c r="A177" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B177" s="6"/>
+      <c r="C177" s="6"/>
+      <c r="D177" s="6"/>
+      <c r="E177" s="6"/>
+      <c r="F177" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="G177" s="6"/>
+      <c r="H177" s="6"/>
+      <c r="I177" s="6"/>
+      <c r="J177" s="6"/>
+      <c r="K177" s="6"/>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A178" s="5"/>
-      <c r="B178" s="5"/>
-      <c r="C178" s="5"/>
-      <c r="D178" s="5"/>
-      <c r="E178" s="5"/>
-      <c r="F178" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="G178" s="5"/>
-      <c r="H178" s="5"/>
-      <c r="I178" s="5"/>
-      <c r="J178" s="5"/>
-      <c r="K178" s="5"/>
+      <c r="A178" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B178" s="6"/>
+      <c r="C178" s="6"/>
+      <c r="D178" s="6"/>
+      <c r="E178" s="6"/>
+      <c r="F178" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="G178" s="6"/>
+      <c r="H178" s="6"/>
+      <c r="I178" s="6"/>
+      <c r="J178" s="6"/>
+      <c r="K178" s="6"/>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A179" s="5"/>
-      <c r="B179" s="5"/>
-      <c r="C179" s="5"/>
-      <c r="D179" s="5"/>
-      <c r="E179" s="5"/>
-      <c r="F179" s="5"/>
-      <c r="G179" s="5"/>
-      <c r="H179" s="5"/>
-      <c r="I179" s="5"/>
-      <c r="J179" s="5"/>
-      <c r="K179" s="5"/>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A180" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B180" s="5"/>
-      <c r="C180" s="5"/>
-      <c r="D180" s="5"/>
-      <c r="E180" s="5"/>
-      <c r="F180" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="G180" s="5"/>
-      <c r="H180" s="5"/>
-      <c r="I180" s="5"/>
-      <c r="J180" s="5"/>
-      <c r="K180" s="5"/>
+      <c r="A179" s="6"/>
+      <c r="B179" s="6"/>
+      <c r="C179" s="6"/>
+      <c r="D179" s="6"/>
+      <c r="E179" s="6"/>
+      <c r="F179" s="6"/>
+      <c r="G179" s="6"/>
+      <c r="H179" s="6"/>
+      <c r="I179" s="6"/>
+      <c r="J179" s="6"/>
+      <c r="K179" s="6"/>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A181" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B181" s="5"/>
-      <c r="C181" s="5"/>
-      <c r="D181" s="5"/>
-      <c r="E181" s="5"/>
-      <c r="F181" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="G181" s="5"/>
-      <c r="H181" s="5"/>
-      <c r="I181" s="5"/>
-      <c r="J181" s="5"/>
-      <c r="K181" s="5"/>
+      <c r="A181" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B181" s="8"/>
+      <c r="C181" s="8"/>
+      <c r="D181" s="8"/>
+      <c r="E181" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="F181" s="8"/>
+      <c r="G181" s="8"/>
+      <c r="H181" s="8"/>
+      <c r="I181" s="8"/>
+      <c r="J181" s="8"/>
+      <c r="K181" s="8"/>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A182" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="B182" s="5"/>
-      <c r="C182" s="5"/>
-      <c r="D182" s="5"/>
-      <c r="E182" s="5"/>
-      <c r="F182" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="G182" s="5"/>
-      <c r="H182" s="5"/>
-      <c r="I182" s="5"/>
-      <c r="J182" s="5"/>
-      <c r="K182" s="5"/>
+      <c r="A182" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B182" s="8"/>
+      <c r="C182" s="8"/>
+      <c r="D182" s="8"/>
+      <c r="E182" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F182" s="8"/>
+      <c r="G182" s="8"/>
+      <c r="H182" s="8"/>
+      <c r="I182" s="8"/>
+      <c r="J182" s="8"/>
+      <c r="K182" s="8"/>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A183" s="5"/>
-      <c r="B183" s="5"/>
-      <c r="C183" s="5"/>
-      <c r="D183" s="5"/>
-      <c r="E183" s="5"/>
-      <c r="F183" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="G183" s="5"/>
-      <c r="H183" s="5"/>
-      <c r="I183" s="5"/>
-      <c r="J183" s="5"/>
-      <c r="K183" s="5"/>
+      <c r="A183" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B183" s="8"/>
+      <c r="C183" s="8"/>
+      <c r="D183" s="8"/>
+      <c r="E183" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F183" s="8"/>
+      <c r="G183" s="8"/>
+      <c r="H183" s="8"/>
+      <c r="I183" s="8"/>
+      <c r="J183" s="8"/>
+      <c r="K183" s="8"/>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A184" s="5"/>
-      <c r="B184" s="5"/>
-      <c r="C184" s="5"/>
-      <c r="D184" s="5"/>
-      <c r="E184" s="5"/>
-      <c r="F184" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="G184" s="5"/>
-      <c r="H184" s="5"/>
-      <c r="I184" s="5"/>
-      <c r="J184" s="5"/>
-      <c r="K184" s="5"/>
+      <c r="A184" s="8"/>
+      <c r="B184" s="8"/>
+      <c r="C184" s="8"/>
+      <c r="D184" s="8"/>
+      <c r="E184" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F184" s="8"/>
+      <c r="G184" s="8"/>
+      <c r="H184" s="8"/>
+      <c r="I184" s="8"/>
+      <c r="J184" s="8"/>
+      <c r="K184" s="8"/>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A186" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B186" s="9"/>
+      <c r="C186" s="9"/>
+      <c r="D186" s="9"/>
+      <c r="E186" s="9"/>
+      <c r="F186" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="G186" s="9"/>
+      <c r="H186" s="9"/>
+      <c r="I186" s="9"/>
+      <c r="J186" s="9"/>
+      <c r="K186" s="9"/>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A187" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B187" s="6"/>
-      <c r="C187" s="6"/>
-      <c r="D187" s="6"/>
-      <c r="E187" s="6"/>
-      <c r="F187" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="G187" s="6"/>
-      <c r="H187" s="6"/>
-      <c r="I187" s="6"/>
-      <c r="J187" s="6"/>
-      <c r="K187" s="6"/>
+      <c r="A187" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B187" s="9"/>
+      <c r="C187" s="9"/>
+      <c r="D187" s="9"/>
+      <c r="E187" s="9"/>
+      <c r="F187" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="G187" s="9"/>
+      <c r="H187" s="9"/>
+      <c r="I187" s="9"/>
+      <c r="J187" s="9"/>
+      <c r="K187" s="9"/>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A188" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B188" s="6"/>
-      <c r="C188" s="6"/>
-      <c r="D188" s="6"/>
-      <c r="E188" s="6"/>
-      <c r="F188" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="G188" s="6"/>
-      <c r="H188" s="6"/>
-      <c r="I188" s="6"/>
-      <c r="J188" s="6"/>
-      <c r="K188" s="6"/>
+      <c r="A188" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B188" s="9"/>
+      <c r="C188" s="9"/>
+      <c r="D188" s="9"/>
+      <c r="E188" s="9"/>
+      <c r="F188" s="9"/>
+      <c r="G188" s="9"/>
+      <c r="H188" s="9"/>
+      <c r="I188" s="9"/>
+      <c r="J188" s="9"/>
+      <c r="K188" s="9"/>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A189" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B189" s="6"/>
-      <c r="C189" s="6"/>
-      <c r="D189" s="6"/>
-      <c r="E189" s="6"/>
-      <c r="F189" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="G189" s="6"/>
-      <c r="H189" s="6"/>
-      <c r="I189" s="6"/>
-      <c r="J189" s="6"/>
-      <c r="K189" s="6"/>
+      <c r="A189" s="9"/>
+      <c r="B189" s="9"/>
+      <c r="C189" s="9"/>
+      <c r="D189" s="9"/>
+      <c r="E189" s="9"/>
+      <c r="F189" s="9"/>
+      <c r="G189" s="9"/>
+      <c r="H189" s="9"/>
+      <c r="I189" s="9"/>
+      <c r="J189" s="9"/>
+      <c r="K189" s="9"/>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A190" s="6"/>
-      <c r="B190" s="6"/>
-      <c r="C190" s="6"/>
-      <c r="D190" s="6"/>
-      <c r="E190" s="6"/>
-      <c r="F190" s="6"/>
-      <c r="G190" s="6"/>
-      <c r="H190" s="6"/>
-      <c r="I190" s="6"/>
-      <c r="J190" s="6"/>
-      <c r="K190" s="6"/>
+      <c r="A190" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B190" s="9"/>
+      <c r="C190" s="9"/>
+      <c r="D190" s="9"/>
+      <c r="E190" s="9"/>
+      <c r="F190" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="G190" s="9"/>
+      <c r="H190" s="9"/>
+      <c r="I190" s="9"/>
+      <c r="J190" s="9"/>
+      <c r="K190" s="9"/>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A191" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B191" s="9"/>
+      <c r="C191" s="9"/>
+      <c r="D191" s="9"/>
+      <c r="E191" s="9"/>
+      <c r="F191" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="G191" s="9"/>
+      <c r="H191" s="9"/>
+      <c r="I191" s="9"/>
+      <c r="J191" s="9"/>
+      <c r="K191" s="9"/>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A192" s="8" t="s">
+      <c r="A192" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B192" s="9"/>
+      <c r="C192" s="9"/>
+      <c r="D192" s="9"/>
+      <c r="E192" s="9"/>
+      <c r="F192" s="9"/>
+      <c r="G192" s="9"/>
+      <c r="H192" s="9"/>
+      <c r="I192" s="9"/>
+      <c r="J192" s="9"/>
+      <c r="K192" s="9"/>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A193" s="9"/>
+      <c r="B193" s="9"/>
+      <c r="C193" s="9"/>
+      <c r="D193" s="9"/>
+      <c r="E193" s="9"/>
+      <c r="F193" s="9"/>
+      <c r="G193" s="9"/>
+      <c r="H193" s="9"/>
+      <c r="I193" s="9"/>
+      <c r="J193" s="9"/>
+      <c r="K193" s="9"/>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A194" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B192" s="8"/>
-      <c r="C192" s="8"/>
-      <c r="D192" s="8"/>
-      <c r="E192" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="F192" s="8"/>
-      <c r="G192" s="8"/>
-      <c r="H192" s="8"/>
-      <c r="I192" s="8"/>
-      <c r="J192" s="8"/>
-      <c r="K192" s="8"/>
-    </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A193" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B193" s="8"/>
-      <c r="C193" s="8"/>
-      <c r="D193" s="8"/>
-      <c r="E193" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="F193" s="8"/>
-      <c r="G193" s="8"/>
-      <c r="H193" s="8"/>
-      <c r="I193" s="8"/>
-      <c r="J193" s="8"/>
-      <c r="K193" s="8"/>
-    </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A194" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B194" s="8"/>
-      <c r="C194" s="8"/>
-      <c r="D194" s="8"/>
-      <c r="E194" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="F194" s="8"/>
-      <c r="G194" s="8"/>
-      <c r="H194" s="8"/>
-      <c r="I194" s="8"/>
-      <c r="J194" s="8"/>
-      <c r="K194" s="8"/>
+      <c r="B194" s="9"/>
+      <c r="C194" s="9"/>
+      <c r="D194" s="9"/>
+      <c r="E194" s="9"/>
+      <c r="F194" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="G194" s="9"/>
+      <c r="H194" s="9"/>
+      <c r="I194" s="9"/>
+      <c r="J194" s="9"/>
+      <c r="K194" s="9"/>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A195" s="8"/>
-      <c r="B195" s="8"/>
-      <c r="C195" s="8"/>
-      <c r="D195" s="8"/>
-      <c r="E195" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="F195" s="8"/>
-      <c r="G195" s="8"/>
-      <c r="H195" s="8"/>
-      <c r="I195" s="8"/>
-      <c r="J195" s="8"/>
-      <c r="K195" s="8"/>
+      <c r="A195" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B195" s="9"/>
+      <c r="C195" s="9"/>
+      <c r="D195" s="9"/>
+      <c r="E195" s="9"/>
+      <c r="F195" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G195" s="9"/>
+      <c r="H195" s="9"/>
+      <c r="I195" s="9"/>
+      <c r="J195" s="9"/>
+      <c r="K195" s="9"/>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A196" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B196" s="9"/>
+      <c r="C196" s="9"/>
+      <c r="D196" s="9"/>
+      <c r="E196" s="9"/>
+      <c r="F196" s="9"/>
+      <c r="G196" s="9"/>
+      <c r="H196" s="9"/>
+      <c r="I196" s="9"/>
+      <c r="J196" s="9"/>
+      <c r="K196" s="9"/>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A197" s="9" t="s">
-        <v>81</v>
-      </c>
+      <c r="A197" s="9"/>
       <c r="B197" s="9"/>
       <c r="C197" s="9"/>
       <c r="D197" s="9"/>
       <c r="E197" s="9"/>
-      <c r="F197" s="9" t="s">
-        <v>132</v>
-      </c>
+      <c r="F197" s="9"/>
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="9"/>
@@ -4089,14 +4131,14 @@
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B198" s="9"/>
       <c r="C198" s="9"/>
       <c r="D198" s="9"/>
       <c r="E198" s="9"/>
       <c r="F198" s="9" t="s">
-        <v>187</v>
+        <v>135</v>
       </c>
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
@@ -4106,13 +4148,15 @@
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" s="9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B199" s="9"/>
       <c r="C199" s="9"/>
       <c r="D199" s="9"/>
       <c r="E199" s="9"/>
-      <c r="F199" s="9"/>
+      <c r="F199" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="9"/>
@@ -4120,7 +4164,9 @@
       <c r="K199" s="9"/>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A200" s="9"/>
+      <c r="A200" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="B200" s="9"/>
       <c r="C200" s="9"/>
       <c r="D200" s="9"/>
@@ -4132,189 +4178,187 @@
       <c r="J200" s="9"/>
       <c r="K200" s="9"/>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A201" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B201" s="9"/>
-      <c r="C201" s="9"/>
-      <c r="D201" s="9"/>
-      <c r="E201" s="9"/>
-      <c r="F201" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="G201" s="9"/>
-      <c r="H201" s="9"/>
-      <c r="I201" s="9"/>
-      <c r="J201" s="9"/>
-      <c r="K201" s="9"/>
-    </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A202" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B202" s="9"/>
-      <c r="C202" s="9"/>
-      <c r="D202" s="9"/>
-      <c r="E202" s="9"/>
-      <c r="F202" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="G202" s="9"/>
-      <c r="H202" s="9"/>
-      <c r="I202" s="9"/>
-      <c r="J202" s="9"/>
-      <c r="K202" s="9"/>
+      <c r="A202" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B202" s="4"/>
+      <c r="C202" s="4"/>
+      <c r="D202" s="4"/>
+      <c r="E202" s="4"/>
+      <c r="F202" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G202" s="4"/>
+      <c r="H202" s="4"/>
+      <c r="I202" s="4"/>
+      <c r="J202" s="4"/>
+      <c r="K202" s="4"/>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A203" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B203" s="9"/>
-      <c r="C203" s="9"/>
-      <c r="D203" s="9"/>
-      <c r="E203" s="9"/>
-      <c r="F203" s="9"/>
-      <c r="G203" s="9"/>
-      <c r="H203" s="9"/>
-      <c r="I203" s="9"/>
-      <c r="J203" s="9"/>
-      <c r="K203" s="9"/>
+      <c r="A203" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B203" s="4"/>
+      <c r="C203" s="4"/>
+      <c r="D203" s="4"/>
+      <c r="E203" s="4"/>
+      <c r="F203" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="G203" s="4"/>
+      <c r="H203" s="4"/>
+      <c r="I203" s="4"/>
+      <c r="J203" s="4"/>
+      <c r="K203" s="4"/>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A204" s="9"/>
-      <c r="B204" s="9"/>
-      <c r="C204" s="9"/>
-      <c r="D204" s="9"/>
-      <c r="E204" s="9"/>
-      <c r="F204" s="9"/>
-      <c r="G204" s="9"/>
-      <c r="H204" s="9"/>
-      <c r="I204" s="9"/>
-      <c r="J204" s="9"/>
-      <c r="K204" s="9"/>
+      <c r="A204" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B204" s="4"/>
+      <c r="C204" s="4"/>
+      <c r="D204" s="4"/>
+      <c r="E204" s="4"/>
+      <c r="F204" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G204" s="4"/>
+      <c r="H204" s="4"/>
+      <c r="I204" s="4"/>
+      <c r="J204" s="4"/>
+      <c r="K204" s="4"/>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A205" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B205" s="9"/>
-      <c r="C205" s="9"/>
-      <c r="D205" s="9"/>
-      <c r="E205" s="9"/>
-      <c r="F205" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="G205" s="9"/>
-      <c r="H205" s="9"/>
-      <c r="I205" s="9"/>
-      <c r="J205" s="9"/>
-      <c r="K205" s="9"/>
+      <c r="A205" s="4"/>
+      <c r="B205" s="4"/>
+      <c r="C205" s="4"/>
+      <c r="D205" s="4"/>
+      <c r="E205" s="4"/>
+      <c r="F205" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G205" s="4"/>
+      <c r="H205" s="4"/>
+      <c r="I205" s="4"/>
+      <c r="J205" s="4"/>
+      <c r="K205" s="4"/>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A206" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B206" s="9"/>
-      <c r="C206" s="9"/>
-      <c r="D206" s="9"/>
-      <c r="E206" s="9"/>
-      <c r="F206" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="G206" s="9"/>
-      <c r="H206" s="9"/>
-      <c r="I206" s="9"/>
-      <c r="J206" s="9"/>
-      <c r="K206" s="9"/>
+      <c r="A206" s="4"/>
+      <c r="B206" s="4"/>
+      <c r="C206" s="4"/>
+      <c r="D206" s="4"/>
+      <c r="E206" s="4"/>
+      <c r="F206" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G206" s="4"/>
+      <c r="H206" s="4"/>
+      <c r="I206" s="4"/>
+      <c r="J206" s="4"/>
+      <c r="K206" s="4"/>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A207" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B207" s="9"/>
-      <c r="C207" s="9"/>
-      <c r="D207" s="9"/>
-      <c r="E207" s="9"/>
-      <c r="F207" s="9"/>
-      <c r="G207" s="9"/>
-      <c r="H207" s="9"/>
-      <c r="I207" s="9"/>
-      <c r="J207" s="9"/>
-      <c r="K207" s="9"/>
+      <c r="A207" s="4"/>
+      <c r="B207" s="4"/>
+      <c r="C207" s="4"/>
+      <c r="D207" s="4"/>
+      <c r="E207" s="4"/>
+      <c r="F207" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="G207" s="4"/>
+      <c r="H207" s="4"/>
+      <c r="I207" s="4"/>
+      <c r="J207" s="4"/>
+      <c r="K207" s="4"/>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A208" s="9"/>
-      <c r="B208" s="9"/>
-      <c r="C208" s="9"/>
-      <c r="D208" s="9"/>
-      <c r="E208" s="9"/>
-      <c r="F208" s="9"/>
-      <c r="G208" s="9"/>
-      <c r="H208" s="9"/>
-      <c r="I208" s="9"/>
-      <c r="J208" s="9"/>
-      <c r="K208" s="9"/>
+      <c r="A208" s="4"/>
+      <c r="B208" s="4"/>
+      <c r="C208" s="4"/>
+      <c r="D208" s="4"/>
+      <c r="E208" s="4"/>
+      <c r="F208" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="G208" s="4"/>
+      <c r="H208" s="4"/>
+      <c r="I208" s="4"/>
+      <c r="J208" s="4"/>
+      <c r="K208" s="4"/>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A209" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B209" s="9"/>
-      <c r="C209" s="9"/>
-      <c r="D209" s="9"/>
-      <c r="E209" s="9"/>
-      <c r="F209" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="G209" s="9"/>
-      <c r="H209" s="9"/>
-      <c r="I209" s="9"/>
-      <c r="J209" s="9"/>
-      <c r="K209" s="9"/>
+      <c r="A209" s="4"/>
+      <c r="B209" s="4"/>
+      <c r="C209" s="4"/>
+      <c r="D209" s="4"/>
+      <c r="E209" s="4"/>
+      <c r="F209" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G209" s="4"/>
+      <c r="H209" s="4"/>
+      <c r="I209" s="4"/>
+      <c r="J209" s="4"/>
+      <c r="K209" s="4"/>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A210" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="B210" s="9"/>
-      <c r="C210" s="9"/>
-      <c r="D210" s="9"/>
-      <c r="E210" s="9"/>
-      <c r="F210" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="G210" s="9"/>
-      <c r="H210" s="9"/>
-      <c r="I210" s="9"/>
-      <c r="J210" s="9"/>
-      <c r="K210" s="9"/>
+      <c r="A210" s="4"/>
+      <c r="B210" s="4"/>
+      <c r="C210" s="4"/>
+      <c r="D210" s="4"/>
+      <c r="E210" s="4"/>
+      <c r="F210" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G210" s="4"/>
+      <c r="H210" s="4"/>
+      <c r="I210" s="4"/>
+      <c r="J210" s="4"/>
+      <c r="K210" s="4"/>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A211" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B211" s="9"/>
-      <c r="C211" s="9"/>
-      <c r="D211" s="9"/>
-      <c r="E211" s="9"/>
-      <c r="F211" s="9"/>
-      <c r="G211" s="9"/>
-      <c r="H211" s="9"/>
-      <c r="I211" s="9"/>
-      <c r="J211" s="9"/>
-      <c r="K211" s="9"/>
+      <c r="A211" s="4"/>
+      <c r="B211" s="4"/>
+      <c r="C211" s="4"/>
+      <c r="D211" s="4"/>
+      <c r="E211" s="4"/>
+      <c r="F211" s="4"/>
+      <c r="G211" s="4"/>
+      <c r="H211" s="4"/>
+      <c r="I211" s="4"/>
+      <c r="J211" s="4"/>
+      <c r="K211" s="4"/>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A212" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B212" s="4"/>
+      <c r="C212" s="4"/>
+      <c r="D212" s="4"/>
+      <c r="E212" s="4"/>
+      <c r="F212" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G212" s="4"/>
+      <c r="H212" s="4"/>
+      <c r="I212" s="4"/>
+      <c r="J212" s="4"/>
+      <c r="K212" s="4"/>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
       <c r="D213" s="4"/>
       <c r="E213" s="4"/>
       <c r="F213" s="4" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="G213" s="4"/>
       <c r="H213" s="4"/>
@@ -4324,14 +4368,14 @@
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
       <c r="D214" s="4"/>
       <c r="E214" s="4"/>
       <c r="F214" s="4" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="G214" s="4"/>
       <c r="H214" s="4"/>
@@ -4340,15 +4384,13 @@
       <c r="K214" s="4"/>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A215" s="4" t="s">
-        <v>160</v>
-      </c>
+      <c r="A215" s="4"/>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
       <c r="D215" s="4"/>
       <c r="E215" s="4"/>
       <c r="F215" s="4" t="s">
-        <v>168</v>
+        <v>116</v>
       </c>
       <c r="G215" s="4"/>
       <c r="H215" s="4"/>
@@ -4363,7 +4405,7 @@
       <c r="D216" s="4"/>
       <c r="E216" s="4"/>
       <c r="F216" s="4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G216" s="4"/>
       <c r="H216" s="4"/>
@@ -4378,7 +4420,7 @@
       <c r="D217" s="4"/>
       <c r="E217" s="4"/>
       <c r="F217" s="4" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="G217" s="4"/>
       <c r="H217" s="4"/>
@@ -4393,7 +4435,7 @@
       <c r="D218" s="4"/>
       <c r="E218" s="4"/>
       <c r="F218" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G218" s="4"/>
       <c r="H218" s="4"/>
@@ -4408,7 +4450,7 @@
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
       <c r="F219" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G219" s="4"/>
       <c r="H219" s="4"/>
@@ -4423,7 +4465,7 @@
       <c r="D220" s="4"/>
       <c r="E220" s="4"/>
       <c r="F220" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G220" s="4"/>
       <c r="H220" s="4"/>
@@ -4437,9 +4479,7 @@
       <c r="C221" s="4"/>
       <c r="D221" s="4"/>
       <c r="E221" s="4"/>
-      <c r="F221" s="4" t="s">
-        <v>231</v>
-      </c>
+      <c r="F221" s="4"/>
       <c r="G221" s="4"/>
       <c r="H221" s="4"/>
       <c r="I221" s="4"/>
@@ -4447,12 +4487,16 @@
       <c r="K221" s="4"/>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A222" s="4"/>
+      <c r="A222" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
       <c r="D222" s="4"/>
       <c r="E222" s="4"/>
-      <c r="F222" s="4"/>
+      <c r="F222" s="4" t="s">
+        <v>213</v>
+      </c>
       <c r="G222" s="4"/>
       <c r="H222" s="4"/>
       <c r="I222" s="4"/>
@@ -4461,14 +4505,14 @@
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
       <c r="F223" s="4" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="G223" s="4"/>
       <c r="H223" s="4"/>
@@ -4478,14 +4522,14 @@
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
       <c r="F224" s="4" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="G224" s="4"/>
       <c r="H224" s="4"/>
@@ -4494,15 +4538,13 @@
       <c r="K224" s="4"/>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A225" s="4" t="s">
-        <v>165</v>
-      </c>
+      <c r="A225" s="4"/>
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
       <c r="D225" s="4"/>
       <c r="E225" s="4"/>
       <c r="F225" s="4" t="s">
-        <v>226</v>
+        <v>120</v>
       </c>
       <c r="G225" s="4"/>
       <c r="H225" s="4"/>
@@ -4517,7 +4559,7 @@
       <c r="D226" s="4"/>
       <c r="E226" s="4"/>
       <c r="F226" s="4" t="s">
-        <v>116</v>
+        <v>198</v>
       </c>
       <c r="G226" s="4"/>
       <c r="H226" s="4"/>
@@ -4532,7 +4574,7 @@
       <c r="D227" s="4"/>
       <c r="E227" s="4"/>
       <c r="F227" s="4" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="G227" s="4"/>
       <c r="H227" s="4"/>
@@ -4547,7 +4589,7 @@
       <c r="D228" s="4"/>
       <c r="E228" s="4"/>
       <c r="F228" s="4" t="s">
-        <v>249</v>
+        <v>217</v>
       </c>
       <c r="G228" s="4"/>
       <c r="H228" s="4"/>
@@ -4562,7 +4604,7 @@
       <c r="D229" s="4"/>
       <c r="E229" s="4"/>
       <c r="F229" s="4" t="s">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G229" s="4"/>
       <c r="H229" s="4"/>
@@ -4577,7 +4619,7 @@
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
       <c r="F230" s="4" t="s">
-        <v>251</v>
+        <v>219</v>
       </c>
       <c r="G230" s="4"/>
       <c r="H230" s="4"/>
@@ -4591,9 +4633,7 @@
       <c r="C231" s="4"/>
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
-      <c r="F231" s="4" t="s">
-        <v>252</v>
-      </c>
+      <c r="F231" s="4"/>
       <c r="G231" s="4"/>
       <c r="H231" s="4"/>
       <c r="I231" s="4"/>
@@ -4601,12 +4641,16 @@
       <c r="K231" s="4"/>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A232" s="4"/>
+      <c r="A232" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
-      <c r="F232" s="4"/>
+      <c r="F232" s="4" t="s">
+        <v>220</v>
+      </c>
       <c r="G232" s="4"/>
       <c r="H232" s="4"/>
       <c r="I232" s="4"/>
@@ -4615,14 +4659,14 @@
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
       <c r="F233" s="4" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="G233" s="4"/>
       <c r="H233" s="4"/>
@@ -4632,14 +4676,14 @@
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
       <c r="D234" s="4"/>
       <c r="E234" s="4"/>
       <c r="F234" s="4" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="G234" s="4"/>
       <c r="H234" s="4"/>
@@ -4648,15 +4692,13 @@
       <c r="K234" s="4"/>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A235" s="4" t="s">
-        <v>166</v>
-      </c>
+      <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
       <c r="F235" s="4" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="G235" s="4"/>
       <c r="H235" s="4"/>
@@ -4671,7 +4713,7 @@
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
       <c r="F236" s="4" t="s">
-        <v>120</v>
+        <v>224</v>
       </c>
       <c r="G236" s="4"/>
       <c r="H236" s="4"/>
@@ -4686,7 +4728,7 @@
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
       <c r="F237" s="4" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="G237" s="4"/>
       <c r="H237" s="4"/>
@@ -4701,7 +4743,7 @@
       <c r="D238" s="4"/>
       <c r="E238" s="4"/>
       <c r="F238" s="4" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G238" s="4"/>
       <c r="H238" s="4"/>
@@ -4716,7 +4758,7 @@
       <c r="D239" s="4"/>
       <c r="E239" s="4"/>
       <c r="F239" s="4" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="G239" s="4"/>
       <c r="H239" s="4"/>
@@ -4731,7 +4773,7 @@
       <c r="D240" s="4"/>
       <c r="E240" s="4"/>
       <c r="F240" s="4" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="G240" s="4"/>
       <c r="H240" s="4"/>
@@ -4739,175 +4781,6 @@
       <c r="J240" s="4"/>
       <c r="K240" s="4"/>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A241" s="4"/>
-      <c r="B241" s="4"/>
-      <c r="C241" s="4"/>
-      <c r="D241" s="4"/>
-      <c r="E241" s="4"/>
-      <c r="F241" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="G241" s="4"/>
-      <c r="H241" s="4"/>
-      <c r="I241" s="4"/>
-      <c r="J241" s="4"/>
-      <c r="K241" s="4"/>
-    </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A242" s="4"/>
-      <c r="B242" s="4"/>
-      <c r="C242" s="4"/>
-      <c r="D242" s="4"/>
-      <c r="E242" s="4"/>
-      <c r="F242" s="4"/>
-      <c r="G242" s="4"/>
-      <c r="H242" s="4"/>
-      <c r="I242" s="4"/>
-      <c r="J242" s="4"/>
-      <c r="K242" s="4"/>
-    </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A243" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B243" s="4"/>
-      <c r="C243" s="4"/>
-      <c r="D243" s="4"/>
-      <c r="E243" s="4"/>
-      <c r="F243" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="G243" s="4"/>
-      <c r="H243" s="4"/>
-      <c r="I243" s="4"/>
-      <c r="J243" s="4"/>
-      <c r="K243" s="4"/>
-    </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A244" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B244" s="4"/>
-      <c r="C244" s="4"/>
-      <c r="D244" s="4"/>
-      <c r="E244" s="4"/>
-      <c r="F244" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="G244" s="4"/>
-      <c r="H244" s="4"/>
-      <c r="I244" s="4"/>
-      <c r="J244" s="4"/>
-      <c r="K244" s="4"/>
-    </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A245" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B245" s="4"/>
-      <c r="C245" s="4"/>
-      <c r="D245" s="4"/>
-      <c r="E245" s="4"/>
-      <c r="F245" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="G245" s="4"/>
-      <c r="H245" s="4"/>
-      <c r="I245" s="4"/>
-      <c r="J245" s="4"/>
-      <c r="K245" s="4"/>
-    </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A246" s="4"/>
-      <c r="B246" s="4"/>
-      <c r="C246" s="4"/>
-      <c r="D246" s="4"/>
-      <c r="E246" s="4"/>
-      <c r="F246" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="G246" s="4"/>
-      <c r="H246" s="4"/>
-      <c r="I246" s="4"/>
-      <c r="J246" s="4"/>
-      <c r="K246" s="4"/>
-    </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A247" s="4"/>
-      <c r="B247" s="4"/>
-      <c r="C247" s="4"/>
-      <c r="D247" s="4"/>
-      <c r="E247" s="4"/>
-      <c r="F247" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="G247" s="4"/>
-      <c r="H247" s="4"/>
-      <c r="I247" s="4"/>
-      <c r="J247" s="4"/>
-      <c r="K247" s="4"/>
-    </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A248" s="4"/>
-      <c r="B248" s="4"/>
-      <c r="C248" s="4"/>
-      <c r="D248" s="4"/>
-      <c r="E248" s="4"/>
-      <c r="F248" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="G248" s="4"/>
-      <c r="H248" s="4"/>
-      <c r="I248" s="4"/>
-      <c r="J248" s="4"/>
-      <c r="K248" s="4"/>
-    </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A249" s="4"/>
-      <c r="B249" s="4"/>
-      <c r="C249" s="4"/>
-      <c r="D249" s="4"/>
-      <c r="E249" s="4"/>
-      <c r="F249" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="G249" s="4"/>
-      <c r="H249" s="4"/>
-      <c r="I249" s="4"/>
-      <c r="J249" s="4"/>
-      <c r="K249" s="4"/>
-    </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A250" s="4"/>
-      <c r="B250" s="4"/>
-      <c r="C250" s="4"/>
-      <c r="D250" s="4"/>
-      <c r="E250" s="4"/>
-      <c r="F250" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="G250" s="4"/>
-      <c r="H250" s="4"/>
-      <c r="I250" s="4"/>
-      <c r="J250" s="4"/>
-      <c r="K250" s="4"/>
-    </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A251" s="4"/>
-      <c r="B251" s="4"/>
-      <c r="C251" s="4"/>
-      <c r="D251" s="4"/>
-      <c r="E251" s="4"/>
-      <c r="F251" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="G251" s="4"/>
-      <c r="H251" s="4"/>
-      <c r="I251" s="4"/>
-      <c r="J251" s="4"/>
-      <c r="K251" s="4"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
